--- a/pages/A787.xlsx
+++ b/pages/A787.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Downloads\PN lookup app\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Downloads\Cabbase\pages\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4FF901B-80F2-4D39-801C-96B3E89C5350}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A62AA60-9E2C-4CAF-A8C8-2946B6263186}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="105">
   <si>
     <t>PART NUMBER (PN)</t>
   </si>
@@ -102,9 +102,6 @@
     <t>1024366-311BHUA / 1024366-311BHU-VAE</t>
   </si>
   <si>
-    <t>TRIM</t>
-  </si>
-  <si>
     <t>832Z6501-1</t>
   </si>
   <si>
@@ -171,9 +168,6 @@
     <t>BACS12FA3K3</t>
   </si>
   <si>
-    <t>BACS12JL3K3</t>
-  </si>
-  <si>
     <t>ESCUTCHEON</t>
   </si>
   <si>
@@ -241,6 +235,117 @@
   </si>
   <si>
     <t>GHẾ IAT 16 GHK (TRỪ TÀU 787-10)</t>
+  </si>
+  <si>
+    <t>THRESHOLD TRIM</t>
+  </si>
+  <si>
+    <t>BAC1522-781-870</t>
+  </si>
+  <si>
+    <t>VERTICAL TRIM (LH)</t>
+  </si>
+  <si>
+    <t>832Z6501-203</t>
+  </si>
+  <si>
+    <t>VERTICAL TRIM (RH)</t>
+  </si>
+  <si>
+    <t>832Z6501-204</t>
+  </si>
+  <si>
+    <t>HORIZONTAL, VERTICAL TRIM (RAW)</t>
+  </si>
+  <si>
+    <t>HORIZONTAL TRIM</t>
+  </si>
+  <si>
+    <t>BAC1522-944-870</t>
+  </si>
+  <si>
+    <t>1044052-005</t>
+  </si>
+  <si>
+    <t>TÚI VẢI ĐỰNG ÁO PHAO</t>
+  </si>
+  <si>
+    <t>787-9
+GHẾ KHÔNG CÓ HỘP IFE</t>
+  </si>
+  <si>
+    <t>1044052-007</t>
+  </si>
+  <si>
+    <t>787-9
+GHẾ CÓ HỘP IFE</t>
+  </si>
+  <si>
+    <t>DÂY STRAP ÁO PHAO</t>
+  </si>
+  <si>
+    <t>1012774-051</t>
+  </si>
+  <si>
+    <t>787-9</t>
+  </si>
+  <si>
+    <t>1003118-005</t>
+  </si>
+  <si>
+    <t>787-10</t>
+  </si>
+  <si>
+    <t>HỘP ĐỰNG ÁO PHAO (ASSY)</t>
+  </si>
+  <si>
+    <t>1030615-011KA01</t>
+  </si>
+  <si>
+    <t>CỬA HỘP ĐỰNG ÁO PHAO</t>
+  </si>
+  <si>
+    <t>1030615-303BUT</t>
+  </si>
+  <si>
+    <t>FOODTRAY LATCH</t>
+  </si>
+  <si>
+    <t>1014252-301BMZ</t>
+  </si>
+  <si>
+    <t>FOODTRAY LATCH ASSY</t>
+  </si>
+  <si>
+    <t>1012222-071KA02</t>
+  </si>
+  <si>
+    <t>SCREW (THAY BACKREST COVER)</t>
+  </si>
+  <si>
+    <t>MS27039-0805</t>
+  </si>
+  <si>
+    <t>CLAMP - TÚI TẠP CHÍ</t>
+  </si>
+  <si>
+    <t>MS25281-F3</t>
+  </si>
+  <si>
+    <t>SPRING - TÚI TẠP CHÍ</t>
+  </si>
+  <si>
+    <t>1012375-001</t>
+  </si>
+  <si>
+    <t>787-9 : HÀNG GHẾ 38ABC, 38GHK
+787-10 : HÀNG GHẾ 54ABC, 54GHK</t>
+  </si>
+  <si>
+    <t>1012375-005</t>
+  </si>
+  <si>
+    <t>CÁC HÀNG GHẾ CÒN LẠI</t>
   </si>
 </sst>
 </file>
@@ -686,11 +791,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="20.28515625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="33.85546875" style="1" customWidth="1"/>
     <col min="3" max="4" width="23" style="2" customWidth="1"/>
     <col min="5" max="5" width="52.5703125" style="1" customWidth="1"/>
     <col min="6" max="16384" width="9.140625" style="1"/>
@@ -730,7 +835,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>7</v>
       </c>
@@ -752,14 +857,14 @@
         <v>7</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>24</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>25</v>
       </c>
       <c r="D4" s="4"/>
       <c r="E4" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -767,14 +872,14 @@
         <v>7</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>24</v>
+        <v>69</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -782,14 +887,14 @@
         <v>7</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>24</v>
+        <v>69</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -797,14 +902,14 @@
         <v>7</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>24</v>
+        <v>69</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="30" x14ac:dyDescent="0.25">
@@ -812,14 +917,14 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>24</v>
+        <v>69</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="30" x14ac:dyDescent="0.25">
@@ -827,14 +932,14 @@
         <v>7</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>24</v>
+        <v>69</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="30" x14ac:dyDescent="0.25">
@@ -842,14 +947,14 @@
         <v>7</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>24</v>
+        <v>69</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="30" x14ac:dyDescent="0.25">
@@ -857,14 +962,14 @@
         <v>7</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>24</v>
+        <v>69</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="30" x14ac:dyDescent="0.25">
@@ -872,10 +977,10 @@
         <v>7</v>
       </c>
       <c r="B12" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C12" s="4" t="s">
         <v>37</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>38</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="3"/>
@@ -885,68 +990,82 @@
         <v>7</v>
       </c>
       <c r="B13" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C13" s="4" t="s">
         <v>43</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>44</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="3"/>
     </row>
     <row r="14" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B14" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C14" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="C14" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>47</v>
-      </c>
+      <c r="D14" s="4"/>
       <c r="E14" s="3"/>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B15" s="3"/>
-      <c r="C15" s="4"/>
+        <v>7</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>70</v>
+      </c>
       <c r="D15" s="4"/>
       <c r="E15" s="3"/>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B16" s="3"/>
-      <c r="C16" s="4"/>
+        <v>7</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>72</v>
+      </c>
       <c r="D16" s="4"/>
       <c r="E16" s="3"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B17" s="3"/>
-      <c r="C17" s="4"/>
+        <v>7</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>74</v>
+      </c>
       <c r="D17" s="4"/>
       <c r="E17" s="3"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B18" s="3"/>
-      <c r="C18" s="4"/>
+        <v>7</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>77</v>
+      </c>
       <c r="D18" s="4"/>
       <c r="E18" s="3"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B19" s="3"/>
       <c r="C19" s="4"/>
@@ -955,7 +1074,7 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B20" s="3"/>
       <c r="C20" s="4"/>
@@ -964,7 +1083,7 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B21" s="3"/>
       <c r="C21" s="4"/>
@@ -973,7 +1092,7 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B22" s="3"/>
       <c r="C22" s="4"/>
@@ -982,12 +1101,93 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B23" s="3"/>
       <c r="C23" s="4"/>
       <c r="D23" s="4"/>
       <c r="E23" s="3"/>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B24" s="3"/>
+      <c r="C24" s="4"/>
+      <c r="D24" s="4"/>
+      <c r="E24" s="3"/>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B25" s="3"/>
+      <c r="C25" s="4"/>
+      <c r="D25" s="4"/>
+      <c r="E25" s="3"/>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B26" s="3"/>
+      <c r="C26" s="4"/>
+      <c r="D26" s="4"/>
+      <c r="E26" s="3"/>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B27" s="3"/>
+      <c r="C27" s="4"/>
+      <c r="D27" s="4"/>
+      <c r="E27" s="3"/>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B28" s="3"/>
+      <c r="C28" s="4"/>
+      <c r="D28" s="4"/>
+      <c r="E28" s="3"/>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B29" s="3"/>
+      <c r="C29" s="4"/>
+      <c r="D29" s="4"/>
+      <c r="E29" s="3"/>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B30" s="3"/>
+      <c r="C30" s="4"/>
+      <c r="D30" s="4"/>
+      <c r="E30" s="3"/>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B31" s="3"/>
+      <c r="C31" s="4"/>
+      <c r="D31" s="4"/>
+      <c r="E31" s="3"/>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B32" s="3"/>
+      <c r="C32" s="4"/>
+      <c r="D32" s="4"/>
+      <c r="E32" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1194,7 +1394,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.140625" customWidth="1"/>
@@ -1273,13 +1473,13 @@
         <v>16</v>
       </c>
       <c r="C4" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="E4" s="13" t="s">
         <v>48</v>
-      </c>
-      <c r="D4" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="E4" s="13" t="s">
-        <v>50</v>
       </c>
       <c r="F4" s="11"/>
     </row>
@@ -1291,14 +1491,14 @@
         <v>16</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E5" s="13"/>
       <c r="F5" s="11" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -1309,14 +1509,14 @@
         <v>16</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E6" s="13"/>
       <c r="F6" s="11" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -1327,13 +1527,13 @@
         <v>16</v>
       </c>
       <c r="C7" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="D7" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="E7" s="13" t="s">
         <v>56</v>
-      </c>
-      <c r="D7" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="E7" s="13" t="s">
-        <v>58</v>
       </c>
       <c r="F7" s="11"/>
     </row>
@@ -1345,14 +1545,14 @@
         <v>16</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E8" s="13"/>
       <c r="F8" s="11" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -1363,14 +1563,14 @@
         <v>16</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E9" s="13"/>
       <c r="F9" s="11" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
@@ -1381,14 +1581,14 @@
         <v>16</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E10" s="13"/>
       <c r="F10" s="11" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -1399,14 +1599,14 @@
         <v>16</v>
       </c>
       <c r="C11" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="D11" s="13" t="s">
         <v>64</v>
-      </c>
-      <c r="D11" s="13" t="s">
-        <v>66</v>
       </c>
       <c r="E11" s="13"/>
       <c r="F11" s="11" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
@@ -1417,127 +1617,313 @@
         <v>16</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E12" s="13"/>
       <c r="F12" s="11" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>7</v>
       </c>
       <c r="B13" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="C13" s="11"/>
-      <c r="D13" s="13"/>
+      <c r="C13" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="D13" s="13" t="s">
+        <v>78</v>
+      </c>
       <c r="E13" s="13"/>
-      <c r="F13" s="11"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F13" s="11" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="B14" s="11"/>
-      <c r="C14" s="11"/>
-      <c r="D14" s="13"/>
+        <v>7</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="D14" s="13" t="s">
+        <v>81</v>
+      </c>
       <c r="E14" s="13"/>
-      <c r="F14" s="11"/>
+      <c r="F14" s="11" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="B15" s="11"/>
-      <c r="C15" s="11"/>
-      <c r="D15" s="13"/>
+        <v>7</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>84</v>
+      </c>
       <c r="E15" s="13"/>
-      <c r="F15" s="11"/>
+      <c r="F15" s="11" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="B16" s="11"/>
-      <c r="C16" s="11"/>
-      <c r="D16" s="13"/>
+        <v>7</v>
+      </c>
+      <c r="B16" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="D16" s="13" t="s">
+        <v>86</v>
+      </c>
       <c r="E16" s="13"/>
-      <c r="F16" s="11"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F16" s="11" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="B17" s="11"/>
-      <c r="C17" s="11"/>
-      <c r="D17" s="13"/>
+        <v>7</v>
+      </c>
+      <c r="B17" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="D17" s="13" t="s">
+        <v>89</v>
+      </c>
       <c r="E17" s="13"/>
-      <c r="F17" s="11"/>
+      <c r="F17" s="11" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="B18" s="11"/>
-      <c r="C18" s="11"/>
-      <c r="D18" s="13"/>
+        <v>7</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="D18" s="13" t="s">
+        <v>91</v>
+      </c>
       <c r="E18" s="13"/>
-      <c r="F18" s="11"/>
+      <c r="F18" s="11" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="B19" s="11"/>
-      <c r="C19" s="11"/>
-      <c r="D19" s="13"/>
+        <v>7</v>
+      </c>
+      <c r="B19" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="D19" s="13" t="s">
+        <v>93</v>
+      </c>
       <c r="E19" s="13"/>
       <c r="F19" s="11"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="B20" s="11"/>
-      <c r="C20" s="11"/>
-      <c r="D20" s="13"/>
+        <v>7</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="D20" s="13" t="s">
+        <v>95</v>
+      </c>
       <c r="E20" s="13"/>
       <c r="F20" s="11"/>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="B21" s="11"/>
-      <c r="C21" s="11"/>
-      <c r="D21" s="13"/>
+        <v>7</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C21" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="D21" s="13" t="s">
+        <v>97</v>
+      </c>
       <c r="E21" s="13"/>
       <c r="F21" s="11"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="B22" s="11"/>
-      <c r="C22" s="11"/>
-      <c r="D22" s="13"/>
+        <v>7</v>
+      </c>
+      <c r="B22" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C22" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>99</v>
+      </c>
       <c r="E22" s="13"/>
       <c r="F22" s="11"/>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="B23" s="11"/>
-      <c r="C23" s="11"/>
-      <c r="D23" s="13"/>
+        <v>7</v>
+      </c>
+      <c r="B23" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C23" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="D23" s="13" t="s">
+        <v>101</v>
+      </c>
       <c r="E23" s="13"/>
-      <c r="F23" s="11"/>
+      <c r="F23" s="11" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B24" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C24" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="D24" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="E24" s="13"/>
+      <c r="F24" s="11" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B25" s="11"/>
+      <c r="C25" s="11"/>
+      <c r="D25" s="13"/>
+      <c r="E25" s="13"/>
+      <c r="F25" s="11"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B26" s="11"/>
+      <c r="C26" s="11"/>
+      <c r="D26" s="13"/>
+      <c r="E26" s="13"/>
+      <c r="F26" s="11"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B27" s="11"/>
+      <c r="C27" s="11"/>
+      <c r="D27" s="13"/>
+      <c r="E27" s="13"/>
+      <c r="F27" s="11"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="B28" s="11"/>
+      <c r="C28" s="11"/>
+      <c r="D28" s="13"/>
+      <c r="E28" s="13"/>
+      <c r="F28" s="11"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="B29" s="11"/>
+      <c r="C29" s="11"/>
+      <c r="D29" s="13"/>
+      <c r="E29" s="13"/>
+      <c r="F29" s="11"/>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="B30" s="11"/>
+      <c r="C30" s="11"/>
+      <c r="D30" s="13"/>
+      <c r="E30" s="13"/>
+      <c r="F30" s="11"/>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="B31" s="11"/>
+      <c r="C31" s="11"/>
+      <c r="D31" s="13"/>
+      <c r="E31" s="13"/>
+      <c r="F31" s="11"/>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="B32" s="11"/>
+      <c r="C32" s="11"/>
+      <c r="D32" s="13"/>
+      <c r="E32" s="13"/>
+      <c r="F32" s="11"/>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="B33" s="11"/>
+      <c r="C33" s="11"/>
+      <c r="D33" s="13"/>
+      <c r="E33" s="13"/>
+      <c r="F33" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/pages/A787.xlsx
+++ b/pages/A787.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Downloads\Cabbase\pages\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A62AA60-9E2C-4CAF-A8C8-2946B6263186}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7074516E-D31C-439D-95BB-9F66BFDD3232}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="105">
   <si>
     <t>PART NUMBER (PN)</t>
   </si>
@@ -972,7 +972,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>7</v>
       </c>
@@ -1011,7 +1011,7 @@
       <c r="D14" s="4"/>
       <c r="E14" s="3"/>
     </row>
-    <row r="15" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>7</v>
       </c>
@@ -1024,7 +1024,7 @@
       <c r="D15" s="4"/>
       <c r="E15" s="3"/>
     </row>
-    <row r="16" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>7</v>
       </c>
@@ -1394,7 +1394,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:F42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.140625" customWidth="1"/>
@@ -1819,7 +1819,7 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B24" s="11" t="s">
         <v>16</v>
@@ -1837,9 +1837,11 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="B25" s="11"/>
+        <v>7</v>
+      </c>
+      <c r="B25" s="11" t="s">
+        <v>16</v>
+      </c>
       <c r="C25" s="11"/>
       <c r="D25" s="13"/>
       <c r="E25" s="13"/>
@@ -1847,9 +1849,11 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="B26" s="11"/>
+        <v>7</v>
+      </c>
+      <c r="B26" s="11" t="s">
+        <v>16</v>
+      </c>
       <c r="C26" s="11"/>
       <c r="D26" s="13"/>
       <c r="E26" s="13"/>
@@ -1857,9 +1861,11 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="B27" s="11"/>
+        <v>7</v>
+      </c>
+      <c r="B27" s="11" t="s">
+        <v>16</v>
+      </c>
       <c r="C27" s="11"/>
       <c r="D27" s="13"/>
       <c r="E27" s="13"/>
@@ -1867,9 +1873,11 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="B28" s="11"/>
+        <v>7</v>
+      </c>
+      <c r="B28" s="11" t="s">
+        <v>16</v>
+      </c>
       <c r="C28" s="11"/>
       <c r="D28" s="13"/>
       <c r="E28" s="13"/>
@@ -1877,9 +1885,11 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="B29" s="11"/>
+        <v>7</v>
+      </c>
+      <c r="B29" s="11" t="s">
+        <v>16</v>
+      </c>
       <c r="C29" s="11"/>
       <c r="D29" s="13"/>
       <c r="E29" s="13"/>
@@ -1887,9 +1897,11 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="B30" s="11"/>
+        <v>7</v>
+      </c>
+      <c r="B30" s="11" t="s">
+        <v>16</v>
+      </c>
       <c r="C30" s="11"/>
       <c r="D30" s="13"/>
       <c r="E30" s="13"/>
@@ -1897,9 +1909,11 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="B31" s="11"/>
+        <v>7</v>
+      </c>
+      <c r="B31" s="11" t="s">
+        <v>16</v>
+      </c>
       <c r="C31" s="11"/>
       <c r="D31" s="13"/>
       <c r="E31" s="13"/>
@@ -1907,9 +1921,11 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="B32" s="11"/>
+        <v>7</v>
+      </c>
+      <c r="B32" s="11" t="s">
+        <v>16</v>
+      </c>
       <c r="C32" s="11"/>
       <c r="D32" s="13"/>
       <c r="E32" s="13"/>
@@ -1917,13 +1933,105 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="B33" s="11"/>
+        <v>7</v>
+      </c>
+      <c r="B33" s="11" t="s">
+        <v>16</v>
+      </c>
       <c r="C33" s="11"/>
       <c r="D33" s="13"/>
       <c r="E33" s="13"/>
       <c r="F33" s="11"/>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B34" s="11"/>
+      <c r="C34" s="11"/>
+      <c r="D34" s="13"/>
+      <c r="E34" s="13"/>
+      <c r="F34" s="11"/>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B35" s="11"/>
+      <c r="C35" s="11"/>
+      <c r="D35" s="13"/>
+      <c r="E35" s="13"/>
+      <c r="F35" s="11"/>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B36" s="11"/>
+      <c r="C36" s="11"/>
+      <c r="D36" s="13"/>
+      <c r="E36" s="13"/>
+      <c r="F36" s="11"/>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="B37" s="11"/>
+      <c r="C37" s="11"/>
+      <c r="D37" s="13"/>
+      <c r="E37" s="13"/>
+      <c r="F37" s="11"/>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="B38" s="11"/>
+      <c r="C38" s="11"/>
+      <c r="D38" s="13"/>
+      <c r="E38" s="13"/>
+      <c r="F38" s="11"/>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="B39" s="11"/>
+      <c r="C39" s="11"/>
+      <c r="D39" s="13"/>
+      <c r="E39" s="13"/>
+      <c r="F39" s="11"/>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="B40" s="11"/>
+      <c r="C40" s="11"/>
+      <c r="D40" s="13"/>
+      <c r="E40" s="13"/>
+      <c r="F40" s="11"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="B41" s="11"/>
+      <c r="C41" s="11"/>
+      <c r="D41" s="13"/>
+      <c r="E41" s="13"/>
+      <c r="F41" s="11"/>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="B42" s="11"/>
+      <c r="C42" s="11"/>
+      <c r="D42" s="13"/>
+      <c r="E42" s="13"/>
+      <c r="F42" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/pages/A787.xlsx
+++ b/pages/A787.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Downloads\Cabbase\pages\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7074516E-D31C-439D-95BB-9F66BFDD3232}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E90C52F-E9E8-4F6F-A9E2-6BCCA6AC3F2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="142">
   <si>
     <t>PART NUMBER (PN)</t>
   </si>
@@ -346,6 +346,124 @@
   </si>
   <si>
     <t>CÁC HÀNG GHẾ CÒN LẠI</t>
+  </si>
+  <si>
+    <t>ENDBAY (787-9)</t>
+  </si>
+  <si>
+    <t>1010210-301BHX</t>
+  </si>
+  <si>
+    <t>1010210-302BHX</t>
+  </si>
+  <si>
+    <t>1010210-321BHX</t>
+  </si>
+  <si>
+    <t>1010210-371BHX</t>
+  </si>
+  <si>
+    <t>1010210-372BHX</t>
+  </si>
+  <si>
+    <t>1010210-375BHX</t>
+  </si>
+  <si>
+    <t>1010210-376BHX</t>
+  </si>
+  <si>
+    <t>17F - 24F, 26F - 40F, 39K (CÓ BUỒNG NGHỈ)
+17F - 31F, 34F - 50F, 47K (KHÔNG CÓ BUỒNG NGHỈ)</t>
+  </si>
+  <si>
+    <t>39A (CÓ BUỒNG NGHỈ)
+47A (KHÔNG CÓ BUỒNG NGHỈ)</t>
+  </si>
+  <si>
+    <t>16F, 25F (CÓ BUỒNG NGHỈ)
+16F, 33F (KHÔNG CÓ BUỒNG NGHỈ)</t>
+  </si>
+  <si>
+    <t>17C - 24C, 27C - 38C, 39C (CÓ BUỒNG NGHỈ)
+17C - 32C, 35C - 46C, 47C (KHÔNG CÓ BUỒNG NGHỈ)</t>
+  </si>
+  <si>
+    <t>17D - 24D, 26D - 40D, 39G (CÓ BUỒNG NGHỈ)
+17D - 31D, 34D - 50D, 47G (KHÔNG CÓ BUỒNG NGHỈ)</t>
+  </si>
+  <si>
+    <t>16C, 26C (CÓ BUỒNG NGHỈ)
+16C, 34C (KHÔNG CÓ BUỒNG NGHỈ)</t>
+  </si>
+  <si>
+    <t>16D, 25D, 16G, 26G (CÓ BUỒNG NGHỈ)
+16D, 33D, 16G, 33G (KHÔNG CÓ BUỒNG NGHỈ)</t>
+  </si>
+  <si>
+    <t>ENDBAY (787-10)</t>
+  </si>
+  <si>
+    <t>55A</t>
+  </si>
+  <si>
+    <t>16F, 21F, 38F</t>
+  </si>
+  <si>
+    <t>17C - 19C, 23C - 37C, 40C - 54C, 55C</t>
+  </si>
+  <si>
+    <t>17F - 20F, 22F - 37F, 39F - 56F, 55K</t>
+  </si>
+  <si>
+    <t>16C, 22C, 39C</t>
+  </si>
+  <si>
+    <t>16D, 21D, 38D, 16G, 22G, 39G</t>
+  </si>
+  <si>
+    <t>17D - 20D, 22D - 37D, 39D - 56D, 55G</t>
+  </si>
+  <si>
+    <t>1010210-301BHXA</t>
+  </si>
+  <si>
+    <t>EPL ASSY</t>
+  </si>
+  <si>
+    <t>1013436-001KA02</t>
+  </si>
+  <si>
+    <t>EPL HOUSING</t>
+  </si>
+  <si>
+    <t>1012857-301BHX</t>
+  </si>
+  <si>
+    <t>1013437-301AVR</t>
+  </si>
+  <si>
+    <t>EPL CLOSEOUT</t>
+  </si>
+  <si>
+    <t>EPL SCREW</t>
+  </si>
+  <si>
+    <t>NAS603-7P</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EPL HOUSING </t>
+  </si>
+  <si>
+    <t>1013029-309AVR</t>
+  </si>
+  <si>
+    <t>GHẾ ĐẦU IAT - D</t>
+  </si>
+  <si>
+    <t>GHẾ ĐẦU IAT - F</t>
+  </si>
+  <si>
+    <t>1013029-313AVR</t>
   </si>
 </sst>
 </file>
@@ -1394,7 +1512,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:F42"/>
+  <dimension ref="A1:F52"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.140625" customWidth="1"/>
@@ -1402,7 +1520,8 @@
     <col min="3" max="3" width="28.42578125" customWidth="1"/>
     <col min="4" max="4" width="23" customWidth="1"/>
     <col min="5" max="5" width="33.7109375" customWidth="1"/>
-    <col min="6" max="6" width="46.42578125" customWidth="1"/>
+    <col min="6" max="6" width="54.85546875" customWidth="1"/>
+    <col min="7" max="7" width="12.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1831,93 +1950,135 @@
         <v>103</v>
       </c>
       <c r="E24" s="13"/>
-      <c r="F24" s="11" t="s">
+      <c r="F24" s="13" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
         <v>7</v>
       </c>
       <c r="B25" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="C25" s="11"/>
-      <c r="D25" s="13"/>
+      <c r="C25" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="D25" s="13" t="s">
+        <v>106</v>
+      </c>
       <c r="E25" s="13"/>
-      <c r="F25" s="11"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F25" s="13" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
         <v>7</v>
       </c>
       <c r="B26" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="C26" s="11"/>
-      <c r="D26" s="13"/>
+      <c r="C26" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="D26" s="13" t="s">
+        <v>107</v>
+      </c>
       <c r="E26" s="13"/>
-      <c r="F26" s="11"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F26" s="13" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
         <v>7</v>
       </c>
       <c r="B27" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="C27" s="11"/>
-      <c r="D27" s="13"/>
+      <c r="C27" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>108</v>
+      </c>
       <c r="E27" s="13"/>
-      <c r="F27" s="11"/>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F27" s="13" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
         <v>7</v>
       </c>
       <c r="B28" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="C28" s="11"/>
-      <c r="D28" s="13"/>
+      <c r="C28" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>109</v>
+      </c>
       <c r="E28" s="13"/>
-      <c r="F28" s="11"/>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F28" s="13" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
         <v>7</v>
       </c>
       <c r="B29" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="C29" s="11"/>
-      <c r="D29" s="13"/>
+      <c r="C29" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="D29" s="13" t="s">
+        <v>110</v>
+      </c>
       <c r="E29" s="13"/>
-      <c r="F29" s="11"/>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F29" s="13" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A30" s="11" t="s">
         <v>7</v>
       </c>
       <c r="B30" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="C30" s="11"/>
-      <c r="D30" s="13"/>
+      <c r="C30" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="D30" s="13" t="s">
+        <v>111</v>
+      </c>
       <c r="E30" s="13"/>
-      <c r="F30" s="11"/>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F30" s="13" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A31" s="11" t="s">
         <v>7</v>
       </c>
       <c r="B31" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="C31" s="11"/>
-      <c r="D31" s="13"/>
+      <c r="C31" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="D31" s="13" t="s">
+        <v>112</v>
+      </c>
       <c r="E31" s="13"/>
-      <c r="F31" s="11"/>
+      <c r="F31" s="13" t="s">
+        <v>119</v>
+      </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="11" t="s">
@@ -1926,10 +2087,18 @@
       <c r="B32" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="C32" s="11"/>
-      <c r="D32" s="13"/>
-      <c r="E32" s="13"/>
-      <c r="F32" s="11"/>
+      <c r="C32" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="D32" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="E32" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="F32" s="11" t="s">
+        <v>124</v>
+      </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="11" t="s">
@@ -1938,100 +2107,294 @@
       <c r="B33" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="C33" s="11"/>
-      <c r="D33" s="13"/>
+      <c r="C33" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="D33" s="13" t="s">
+        <v>107</v>
+      </c>
       <c r="E33" s="13"/>
-      <c r="F33" s="11"/>
+      <c r="F33" s="11" t="s">
+        <v>121</v>
+      </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="B34" s="11"/>
-      <c r="C34" s="11"/>
-      <c r="D34" s="13"/>
+        <v>7</v>
+      </c>
+      <c r="B34" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C34" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="D34" s="13" t="s">
+        <v>108</v>
+      </c>
       <c r="E34" s="13"/>
-      <c r="F34" s="11"/>
+      <c r="F34" s="11" t="s">
+        <v>122</v>
+      </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="B35" s="11"/>
-      <c r="C35" s="11"/>
-      <c r="D35" s="13"/>
+        <v>7</v>
+      </c>
+      <c r="B35" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C35" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="D35" s="13" t="s">
+        <v>109</v>
+      </c>
       <c r="E35" s="13"/>
-      <c r="F35" s="11"/>
+      <c r="F35" s="11" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="B36" s="11"/>
-      <c r="C36" s="11"/>
-      <c r="D36" s="13"/>
+        <v>7</v>
+      </c>
+      <c r="B36" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C36" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="D36" s="13" t="s">
+        <v>110</v>
+      </c>
       <c r="E36" s="13"/>
-      <c r="F36" s="11"/>
+      <c r="F36" s="11" t="s">
+        <v>127</v>
+      </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="B37" s="11"/>
-      <c r="C37" s="11"/>
-      <c r="D37" s="13"/>
+        <v>7</v>
+      </c>
+      <c r="B37" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C37" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="D37" s="13" t="s">
+        <v>111</v>
+      </c>
       <c r="E37" s="13"/>
-      <c r="F37" s="11"/>
+      <c r="F37" s="11" t="s">
+        <v>125</v>
+      </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="B38" s="11"/>
-      <c r="C38" s="11"/>
-      <c r="D38" s="13"/>
+        <v>7</v>
+      </c>
+      <c r="B38" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C38" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="D38" s="13" t="s">
+        <v>112</v>
+      </c>
       <c r="E38" s="13"/>
-      <c r="F38" s="11"/>
+      <c r="F38" s="11" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="B39" s="11"/>
-      <c r="C39" s="11"/>
-      <c r="D39" s="13"/>
+        <v>7</v>
+      </c>
+      <c r="B39" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C39" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="D39" s="13" t="s">
+        <v>130</v>
+      </c>
       <c r="E39" s="13"/>
-      <c r="F39" s="11"/>
+      <c r="F39" s="11" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="B40" s="11"/>
-      <c r="C40" s="11"/>
-      <c r="D40" s="13"/>
+        <v>7</v>
+      </c>
+      <c r="B40" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C40" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="D40" s="13" t="s">
+        <v>132</v>
+      </c>
       <c r="E40" s="13"/>
-      <c r="F40" s="11"/>
+      <c r="F40" s="11" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="B41" s="11"/>
-      <c r="C41" s="11"/>
-      <c r="D41" s="13"/>
+        <v>7</v>
+      </c>
+      <c r="B41" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C41" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="D41" s="13" t="s">
+        <v>133</v>
+      </c>
       <c r="E41" s="13"/>
-      <c r="F41" s="11"/>
+      <c r="F41" s="11" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B42" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C42" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="D42" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="E42" s="13"/>
+      <c r="F42" s="11" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B43" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C43" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="D43" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="E43" s="13"/>
+      <c r="F43" s="11" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B44" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C44" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="D44" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="E44" s="13"/>
+      <c r="F44" s="11" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B45" s="11"/>
+      <c r="C45" s="11"/>
+      <c r="D45" s="13"/>
+      <c r="E45" s="13"/>
+      <c r="F45" s="11"/>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B46" s="11"/>
+      <c r="C46" s="11"/>
+      <c r="D46" s="13"/>
+      <c r="E46" s="13"/>
+      <c r="F46" s="11"/>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="B42" s="11"/>
-      <c r="C42" s="11"/>
-      <c r="D42" s="13"/>
-      <c r="E42" s="13"/>
-      <c r="F42" s="11"/>
+      <c r="B47" s="11"/>
+      <c r="C47" s="11"/>
+      <c r="D47" s="13"/>
+      <c r="E47" s="13"/>
+      <c r="F47" s="11"/>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="B48" s="11"/>
+      <c r="C48" s="11"/>
+      <c r="D48" s="13"/>
+      <c r="E48" s="13"/>
+      <c r="F48" s="11"/>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="B49" s="11"/>
+      <c r="C49" s="11"/>
+      <c r="D49" s="13"/>
+      <c r="E49" s="13"/>
+      <c r="F49" s="11"/>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="B50" s="11"/>
+      <c r="C50" s="11"/>
+      <c r="D50" s="13"/>
+      <c r="E50" s="13"/>
+      <c r="F50" s="11"/>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="B51" s="11"/>
+      <c r="C51" s="11"/>
+      <c r="D51" s="13"/>
+      <c r="E51" s="13"/>
+      <c r="F51" s="11"/>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="B52" s="11"/>
+      <c r="C52" s="11"/>
+      <c r="D52" s="13"/>
+      <c r="E52" s="13"/>
+      <c r="F52" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/pages/A787.xlsx
+++ b/pages/A787.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Downloads\Cabbase\pages\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E90C52F-E9E8-4F6F-A9E2-6BCCA6AC3F2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E92EEA46-A330-421A-9AA5-2BFC8E69F63F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="139">
   <si>
     <t>PART NUMBER (PN)</t>
   </si>
@@ -436,9 +436,6 @@
     <t>EPL HOUSING</t>
   </si>
   <si>
-    <t>1012857-301BHX</t>
-  </si>
-  <si>
     <t>1013437-301AVR</t>
   </si>
   <si>
@@ -451,19 +448,17 @@
     <t>NAS603-7P</t>
   </si>
   <si>
-    <t xml:space="preserve">EPL HOUSING </t>
-  </si>
-  <si>
-    <t>1013029-309AVR</t>
-  </si>
-  <si>
-    <t>GHẾ ĐẦU IAT - D</t>
-  </si>
-  <si>
-    <t>GHẾ ĐẦU IAT - F</t>
-  </si>
-  <si>
-    <t>1013029-313AVR</t>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>1012857-301BHX
+1013029-309AVR
+1013029-313AVR</t>
+  </si>
+  <si>
+    <t>GHẾ THƯỜNG
+GHẾ ĐẦU IAT - F
+GHẾ ĐẦU IAT - D</t>
   </si>
 </sst>
 </file>
@@ -1512,7 +1507,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:F52"/>
+  <dimension ref="A1:F50"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.140625" customWidth="1"/>
@@ -2226,7 +2221,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" ht="42.75" x14ac:dyDescent="0.25">
       <c r="A40" s="11" t="s">
         <v>7</v>
       </c>
@@ -2237,11 +2232,11 @@
         <v>131</v>
       </c>
       <c r="D40" s="13" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="E40" s="13"/>
       <c r="F40" s="11" t="s">
-        <v>61</v>
+        <v>138</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -2252,15 +2247,13 @@
         <v>16</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D41" s="13" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E41" s="13"/>
-      <c r="F41" s="11" t="s">
-        <v>61</v>
-      </c>
+      <c r="F41" s="11"/>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="11" t="s">
@@ -2270,55 +2263,39 @@
         <v>16</v>
       </c>
       <c r="C42" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="D42" s="13" t="s">
         <v>135</v>
       </c>
-      <c r="D42" s="13" t="s">
-        <v>136</v>
-      </c>
       <c r="E42" s="13"/>
-      <c r="F42" s="11" t="s">
-        <v>61</v>
-      </c>
+      <c r="F42" s="11"/>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B43" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C43" s="11" t="s">
-        <v>137</v>
-      </c>
-      <c r="D43" s="13" t="s">
-        <v>138</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="B43" s="11"/>
+      <c r="C43" s="11"/>
+      <c r="D43" s="13"/>
       <c r="E43" s="13"/>
-      <c r="F43" s="11" t="s">
-        <v>140</v>
-      </c>
+      <c r="F43" s="11"/>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B44" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C44" s="11" t="s">
-        <v>137</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="B44" s="11"/>
+      <c r="C44" s="11"/>
       <c r="D44" s="13" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="E44" s="13"/>
-      <c r="F44" s="11" t="s">
-        <v>139</v>
-      </c>
+      <c r="F44" s="11"/>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="11" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B45" s="11"/>
       <c r="C45" s="11"/>
@@ -2328,7 +2305,7 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="11" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B46" s="11"/>
       <c r="C46" s="11"/>
@@ -2375,26 +2352,6 @@
       <c r="D50" s="13"/>
       <c r="E50" s="13"/>
       <c r="F50" s="11"/>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="B51" s="11"/>
-      <c r="C51" s="11"/>
-      <c r="D51" s="13"/>
-      <c r="E51" s="13"/>
-      <c r="F51" s="11"/>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="B52" s="11"/>
-      <c r="C52" s="11"/>
-      <c r="D52" s="13"/>
-      <c r="E52" s="13"/>
-      <c r="F52" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/pages/A787.xlsx
+++ b/pages/A787.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Downloads\Cabbase\pages\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E92EEA46-A330-421A-9AA5-2BFC8E69F63F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1A420AD-5B60-4B99-8747-7EC0BAD38335}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="142">
   <si>
     <t>PART NUMBER (PN)</t>
   </si>
@@ -388,10 +388,6 @@
 17C - 32C, 35C - 46C, 47C (KHÔNG CÓ BUỒNG NGHỈ)</t>
   </si>
   <si>
-    <t>17D - 24D, 26D - 40D, 39G (CÓ BUỒNG NGHỈ)
-17D - 31D, 34D - 50D, 47G (KHÔNG CÓ BUỒNG NGHỈ)</t>
-  </si>
-  <si>
     <t>16C, 26C (CÓ BUỒNG NGHỈ)
 16C, 34C (KHÔNG CÓ BUỒNG NGHỈ)</t>
   </si>
@@ -421,9 +417,6 @@
     <t>16D, 21D, 38D, 16G, 22G, 39G</t>
   </si>
   <si>
-    <t>17D - 20D, 22D - 37D, 39D - 56D, 55G</t>
-  </si>
-  <si>
     <t>1010210-301BHXA</t>
   </si>
   <si>
@@ -436,6 +429,9 @@
     <t>EPL HOUSING</t>
   </si>
   <si>
+    <t>1012857-301BHX</t>
+  </si>
+  <si>
     <t>1013437-301AVR</t>
   </si>
   <si>
@@ -448,17 +444,26 @@
     <t>NAS603-7P</t>
   </si>
   <si>
+    <t>1013029-309AVR</t>
+  </si>
+  <si>
+    <t>GHẾ ĐẦU IAT - D</t>
+  </si>
+  <si>
+    <t>GHẾ ĐẦU IAT - F</t>
+  </si>
+  <si>
+    <t>1013029-313AVR</t>
+  </si>
+  <si>
     <t xml:space="preserve"> </t>
   </si>
   <si>
-    <t>1012857-301BHX
-1013029-309AVR
-1013029-313AVR</t>
-  </si>
-  <si>
-    <t>GHẾ THƯỜNG
-GHẾ ĐẦU IAT - F
-GHẾ ĐẦU IAT - D</t>
+    <t>17D - 24D, 26D - 40D, 17G - 24G, 27G - 38G, 39G (CÓ BUỒNG NGHỈ)
+17D - 31D, 34D - 50D, 17G - 31G, 35G - 46G, 47G (KHÔNG CÓ BUỒNG NGHỈ)</t>
+  </si>
+  <si>
+    <t>17D - 20D, 22D - 37D, 39D - 56D, 17G - 19G, 23G - 37G, 40G - 54G, 55G</t>
   </si>
 </sst>
 </file>
@@ -1507,7 +1512,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:F50"/>
+  <dimension ref="A1:F52"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.140625" customWidth="1"/>
@@ -2021,7 +2026,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" ht="57" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
         <v>7</v>
       </c>
@@ -2036,7 +2041,7 @@
       </c>
       <c r="E29" s="13"/>
       <c r="F29" s="13" t="s">
-        <v>117</v>
+        <v>140</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
@@ -2054,7 +2059,7 @@
       </c>
       <c r="E30" s="13"/>
       <c r="F30" s="13" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
@@ -2072,7 +2077,7 @@
       </c>
       <c r="E31" s="13"/>
       <c r="F31" s="13" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -2083,16 +2088,16 @@
         <v>16</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D32" s="13" t="s">
         <v>106</v>
       </c>
       <c r="E32" s="13" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F32" s="11" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -2103,14 +2108,14 @@
         <v>16</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D33" s="13" t="s">
         <v>107</v>
       </c>
       <c r="E33" s="13"/>
       <c r="F33" s="11" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -2121,14 +2126,14 @@
         <v>16</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D34" s="13" t="s">
         <v>108</v>
       </c>
       <c r="E34" s="13"/>
       <c r="F34" s="11" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -2139,17 +2144,17 @@
         <v>16</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D35" s="13" t="s">
         <v>109</v>
       </c>
       <c r="E35" s="13"/>
       <c r="F35" s="11" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A36" s="11" t="s">
         <v>7</v>
       </c>
@@ -2157,14 +2162,14 @@
         <v>16</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D36" s="13" t="s">
         <v>110</v>
       </c>
       <c r="E36" s="13"/>
       <c r="F36" s="11" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -2175,14 +2180,14 @@
         <v>16</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D37" s="13" t="s">
         <v>111</v>
       </c>
       <c r="E37" s="13"/>
       <c r="F37" s="11" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -2193,14 +2198,14 @@
         <v>16</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D38" s="13" t="s">
         <v>112</v>
       </c>
       <c r="E38" s="13"/>
       <c r="F38" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -2211,17 +2216,17 @@
         <v>16</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D39" s="13" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E39" s="13"/>
       <c r="F39" s="11" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="40" spans="1:6" ht="42.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="11" t="s">
         <v>7</v>
       </c>
@@ -2229,14 +2234,14 @@
         <v>16</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D40" s="13" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="E40" s="13"/>
       <c r="F40" s="11" t="s">
-        <v>138</v>
+        <v>61</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -2247,13 +2252,15 @@
         <v>16</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="D41" s="13" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="E41" s="13"/>
-      <c r="F41" s="11"/>
+      <c r="F41" s="11" t="s">
+        <v>137</v>
+      </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="11" t="s">
@@ -2263,39 +2270,51 @@
         <v>16</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="D42" s="13" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="E42" s="13"/>
-      <c r="F42" s="11"/>
+      <c r="F42" s="11" t="s">
+        <v>136</v>
+      </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="B43" s="11"/>
-      <c r="C43" s="11"/>
-      <c r="D43" s="13"/>
+        <v>7</v>
+      </c>
+      <c r="B43" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C43" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="D43" s="13" t="s">
+        <v>131</v>
+      </c>
       <c r="E43" s="13"/>
       <c r="F43" s="11"/>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="B44" s="11"/>
-      <c r="C44" s="11"/>
+        <v>7</v>
+      </c>
+      <c r="B44" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C44" s="11" t="s">
+        <v>133</v>
+      </c>
       <c r="D44" s="13" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E44" s="13"/>
       <c r="F44" s="11"/>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="11" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B45" s="11"/>
       <c r="C45" s="11"/>
@@ -2305,11 +2324,13 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="11" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B46" s="11"/>
       <c r="C46" s="11"/>
-      <c r="D46" s="13"/>
+      <c r="D46" s="13" t="s">
+        <v>139</v>
+      </c>
       <c r="E46" s="13"/>
       <c r="F46" s="11"/>
     </row>
@@ -2352,6 +2373,26 @@
       <c r="D50" s="13"/>
       <c r="E50" s="13"/>
       <c r="F50" s="11"/>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="B51" s="11"/>
+      <c r="C51" s="11"/>
+      <c r="D51" s="13"/>
+      <c r="E51" s="13"/>
+      <c r="F51" s="11"/>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="B52" s="11"/>
+      <c r="C52" s="11"/>
+      <c r="D52" s="13"/>
+      <c r="E52" s="13"/>
+      <c r="F52" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/pages/A787.xlsx
+++ b/pages/A787.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Downloads\Cabbase\pages\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1A420AD-5B60-4B99-8747-7EC0BAD38335}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CEF5841-BD65-4407-87BE-B5B8007E2A21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="146">
   <si>
     <t>PART NUMBER (PN)</t>
   </si>
@@ -456,14 +456,26 @@
     <t>1013029-313AVR</t>
   </si>
   <si>
-    <t xml:space="preserve"> </t>
-  </si>
-  <si>
     <t>17D - 24D, 26D - 40D, 17G - 24G, 27G - 38G, 39G (CÓ BUỒNG NGHỈ)
 17D - 31D, 34D - 50D, 17G - 31G, 35G - 46G, 47G (KHÔNG CÓ BUỒNG NGHỈ)</t>
   </si>
   <si>
     <t>17D - 20D, 22D - 37D, 39D - 56D, 17G - 19G, 23G - 37G, 40G - 54G, 55G</t>
+  </si>
+  <si>
+    <t>TRACK FITTING</t>
+  </si>
+  <si>
+    <t>H3-1904-1</t>
+  </si>
+  <si>
+    <t>FWD</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> H3-1903-100</t>
+  </si>
+  <si>
+    <t>AFT</t>
   </si>
 </sst>
 </file>
@@ -2041,7 +2053,7 @@
       </c>
       <c r="E29" s="13"/>
       <c r="F29" s="13" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
@@ -2169,7 +2181,7 @@
       </c>
       <c r="E36" s="13"/>
       <c r="F36" s="11" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -2314,25 +2326,39 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="B45" s="11"/>
-      <c r="C45" s="11"/>
-      <c r="D45" s="13"/>
+        <v>7</v>
+      </c>
+      <c r="B45" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C45" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="D45" s="13" t="s">
+        <v>142</v>
+      </c>
       <c r="E45" s="13"/>
-      <c r="F45" s="11"/>
+      <c r="F45" s="11" t="s">
+        <v>143</v>
+      </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="B46" s="11"/>
-      <c r="C46" s="11"/>
+        <v>7</v>
+      </c>
+      <c r="B46" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C46" s="11" t="s">
+        <v>141</v>
+      </c>
       <c r="D46" s="13" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="E46" s="13"/>
-      <c r="F46" s="11"/>
+      <c r="F46" s="11" t="s">
+        <v>145</v>
+      </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="11" t="s">

--- a/pages/A787.xlsx
+++ b/pages/A787.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Downloads\Cabbase\pages\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CEF5841-BD65-4407-87BE-B5B8007E2A21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DBA160C-FD40-4E9D-8232-A20AF20B7D7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="197">
   <si>
     <t>PART NUMBER (PN)</t>
   </si>
@@ -199,9 +199,6 @@
   </si>
   <si>
     <t>1011535-005</t>
-  </si>
-  <si>
-    <t>NÚT BẤM RECLINE</t>
   </si>
   <si>
     <t>SP23997C29</t>
@@ -405,9 +402,6 @@
     <t>16F, 21F, 38F</t>
   </si>
   <si>
-    <t>17C - 19C, 23C - 37C, 40C - 54C, 55C</t>
-  </si>
-  <si>
     <t>17F - 20F, 22F - 37F, 39F - 56F, 55K</t>
   </si>
   <si>
@@ -456,13 +450,6 @@
     <t>1013029-313AVR</t>
   </si>
   <si>
-    <t>17D - 24D, 26D - 40D, 17G - 24G, 27G - 38G, 39G (CÓ BUỒNG NGHỈ)
-17D - 31D, 34D - 50D, 17G - 31G, 35G - 46G, 47G (KHÔNG CÓ BUỒNG NGHỈ)</t>
-  </si>
-  <si>
-    <t>17D - 20D, 22D - 37D, 39D - 56D, 17G - 19G, 23G - 37G, 40G - 54G, 55G</t>
-  </si>
-  <si>
     <t>TRACK FITTING</t>
   </si>
   <si>
@@ -476,6 +463,172 @@
   </si>
   <si>
     <t>AFT</t>
+  </si>
+  <si>
+    <t>17C - 19C, 23C - 37C, 40C - 55C</t>
+  </si>
+  <si>
+    <t>17D - 20D, 22D - 37D, 39D - 56D, 17G - 19G, 23G - 37G, 40G - 55G</t>
+  </si>
+  <si>
+    <t>17D - 24D, 26D - 40D, 17G - 24G, 27G - 39G (CÓ BUỒNG NGHỈ)
+17D - 31D, 34D - 50D, 17G - 31G, 35G - 47G (KHÔNG CÓ BUỒNG NGHỈ)</t>
+  </si>
+  <si>
+    <t>C SEAT</t>
+  </si>
+  <si>
+    <t>TRACKING ACTUATOR</t>
+  </si>
+  <si>
+    <t>LPB663</t>
+  </si>
+  <si>
+    <t>RECLINE ACTUATOR</t>
+  </si>
+  <si>
+    <t>RPB1110</t>
+  </si>
+  <si>
+    <t>FRONT FAIRING (WITH LIFEVEST BOX)</t>
+  </si>
+  <si>
+    <t>F0477895</t>
+  </si>
+  <si>
+    <t>LIFEVEST DOOR</t>
+  </si>
+  <si>
+    <t>F0477899</t>
+  </si>
+  <si>
+    <t>LIFEVEST STRAP</t>
+  </si>
+  <si>
+    <t>F0493938</t>
+  </si>
+  <si>
+    <t>ECBB</t>
+  </si>
+  <si>
+    <t>F0466795</t>
+  </si>
+  <si>
+    <t>ECBB1116</t>
+  </si>
+  <si>
+    <t>KDB</t>
+  </si>
+  <si>
+    <t>F0409675</t>
+  </si>
+  <si>
+    <t>FITTING COVER</t>
+  </si>
+  <si>
+    <t>1877910-1</t>
+  </si>
+  <si>
+    <t>F355952</t>
+  </si>
+  <si>
+    <t>1877910-2</t>
+  </si>
+  <si>
+    <t>F0424691</t>
+  </si>
+  <si>
+    <t>EMA</t>
+  </si>
+  <si>
+    <t>513766-401-42</t>
+  </si>
+  <si>
+    <t>GHẾ 1ADGK</t>
+  </si>
+  <si>
+    <t>511959-407-42</t>
+  </si>
+  <si>
+    <t>CÁC GHẾ CÒN LẠI</t>
+  </si>
+  <si>
+    <t>INFLATOR</t>
+  </si>
+  <si>
+    <t>510184-401</t>
+  </si>
+  <si>
+    <t>511878-401</t>
+  </si>
+  <si>
+    <t>F0499318</t>
+  </si>
+  <si>
+    <t>GHẾ 1DK</t>
+  </si>
+  <si>
+    <t>7233-1-60115WA4</t>
+  </si>
+  <si>
+    <t>F0499319</t>
+  </si>
+  <si>
+    <t>7233-1-50115WA4</t>
+  </si>
+  <si>
+    <t>GHẾ 1AG</t>
+  </si>
+  <si>
+    <t>RECLINE CABLE</t>
+  </si>
+  <si>
+    <t>F0570160</t>
+  </si>
+  <si>
+    <t>7233-4601A4B</t>
+  </si>
+  <si>
+    <t>BUCKLE HALF ASSY</t>
+  </si>
+  <si>
+    <t>F0570159</t>
+  </si>
+  <si>
+    <t>7233-3501A4B</t>
+  </si>
+  <si>
+    <t>F0570162</t>
+  </si>
+  <si>
+    <t>7233-4201A4B</t>
+  </si>
+  <si>
+    <t>GHẾ 2DK &gt;&gt; 7DK</t>
+  </si>
+  <si>
+    <t>F0570161</t>
+  </si>
+  <si>
+    <t>7233-3101A4B</t>
+  </si>
+  <si>
+    <t>GHẾ 2AG &gt;&gt; 7AG</t>
+  </si>
+  <si>
+    <t>INFLATABLE SEATBELT</t>
+  </si>
+  <si>
+    <t>F0489366</t>
+  </si>
+  <si>
+    <t>7233-1-20115WA4</t>
+  </si>
+  <si>
+    <t>F0489367</t>
+  </si>
+  <si>
+    <t>7233-1-10115WA4</t>
   </si>
 </sst>
 </file>
@@ -987,7 +1140,7 @@
         <v>7</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>24</v>
@@ -1002,7 +1155,7 @@
         <v>7</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>26</v>
@@ -1017,7 +1170,7 @@
         <v>7</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>28</v>
@@ -1032,7 +1185,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>30</v>
@@ -1047,7 +1200,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>25</v>
@@ -1062,7 +1215,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>27</v>
@@ -1077,7 +1230,7 @@
         <v>7</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>29</v>
@@ -1092,7 +1245,7 @@
         <v>7</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>31</v>
@@ -1146,10 +1299,10 @@
         <v>7</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="3"/>
@@ -1159,10 +1312,10 @@
         <v>7</v>
       </c>
       <c r="B16" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C16" s="4" t="s">
         <v>71</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>72</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="3"/>
@@ -1172,10 +1325,10 @@
         <v>7</v>
       </c>
       <c r="B17" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C17" s="4" t="s">
         <v>73</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>74</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="3"/>
@@ -1185,10 +1338,10 @@
         <v>7</v>
       </c>
       <c r="B18" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C18" s="4" t="s">
         <v>76</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>77</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="3"/>
@@ -1524,7 +1677,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:F52"/>
+  <dimension ref="A1:F76"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.140625" customWidth="1"/>
@@ -1676,14 +1829,14 @@
         <v>16</v>
       </c>
       <c r="C8" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="D8" s="13" t="s">
         <v>57</v>
-      </c>
-      <c r="D8" s="13" t="s">
-        <v>58</v>
       </c>
       <c r="E8" s="13"/>
       <c r="F8" s="11" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -1694,32 +1847,32 @@
         <v>16</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>57</v>
+        <v>180</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E9" s="13"/>
       <c r="F9" s="11" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="11" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
-      <c r="A10" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B10" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" s="11" t="s">
+      <c r="D10" s="13" t="s">
         <v>62</v>
-      </c>
-      <c r="D10" s="13" t="s">
-        <v>63</v>
       </c>
       <c r="E10" s="13"/>
       <c r="F10" s="11" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -1730,14 +1883,14 @@
         <v>16</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E11" s="13"/>
       <c r="F11" s="11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
@@ -1748,14 +1901,14 @@
         <v>16</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E12" s="13"/>
       <c r="F12" s="11" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
@@ -1766,14 +1919,14 @@
         <v>16</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E13" s="13"/>
       <c r="F13" s="11" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
@@ -1784,14 +1937,14 @@
         <v>16</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E14" s="13"/>
       <c r="F14" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -1802,14 +1955,14 @@
         <v>16</v>
       </c>
       <c r="C15" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="D15" s="13" t="s">
         <v>83</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>84</v>
       </c>
       <c r="E15" s="13"/>
       <c r="F15" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -1820,14 +1973,14 @@
         <v>16</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E16" s="13"/>
       <c r="F16" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
@@ -1838,14 +1991,14 @@
         <v>16</v>
       </c>
       <c r="C17" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="D17" s="13" t="s">
         <v>88</v>
-      </c>
-      <c r="D17" s="13" t="s">
-        <v>89</v>
       </c>
       <c r="E17" s="13"/>
       <c r="F17" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -1856,14 +2009,14 @@
         <v>16</v>
       </c>
       <c r="C18" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="D18" s="13" t="s">
         <v>90</v>
-      </c>
-      <c r="D18" s="13" t="s">
-        <v>91</v>
       </c>
       <c r="E18" s="13"/>
       <c r="F18" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -1874,10 +2027,10 @@
         <v>16</v>
       </c>
       <c r="C19" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="D19" s="13" t="s">
         <v>92</v>
-      </c>
-      <c r="D19" s="13" t="s">
-        <v>93</v>
       </c>
       <c r="E19" s="13"/>
       <c r="F19" s="11"/>
@@ -1890,10 +2043,10 @@
         <v>16</v>
       </c>
       <c r="C20" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="D20" s="13" t="s">
         <v>94</v>
-      </c>
-      <c r="D20" s="13" t="s">
-        <v>95</v>
       </c>
       <c r="E20" s="13"/>
       <c r="F20" s="11"/>
@@ -1906,10 +2059,10 @@
         <v>16</v>
       </c>
       <c r="C21" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="D21" s="13" t="s">
         <v>96</v>
-      </c>
-      <c r="D21" s="13" t="s">
-        <v>97</v>
       </c>
       <c r="E21" s="13"/>
       <c r="F21" s="11"/>
@@ -1922,10 +2075,10 @@
         <v>16</v>
       </c>
       <c r="C22" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="D22" s="13" t="s">
         <v>98</v>
-      </c>
-      <c r="D22" s="13" t="s">
-        <v>99</v>
       </c>
       <c r="E22" s="13"/>
       <c r="F22" s="11"/>
@@ -1938,14 +2091,14 @@
         <v>16</v>
       </c>
       <c r="C23" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="D23" s="13" t="s">
         <v>100</v>
-      </c>
-      <c r="D23" s="13" t="s">
-        <v>101</v>
       </c>
       <c r="E23" s="13"/>
       <c r="F23" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -1956,14 +2109,14 @@
         <v>16</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D24" s="13" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E24" s="13"/>
       <c r="F24" s="13" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
@@ -1974,14 +2127,14 @@
         <v>16</v>
       </c>
       <c r="C25" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="D25" s="13" t="s">
         <v>105</v>
-      </c>
-      <c r="D25" s="13" t="s">
-        <v>106</v>
       </c>
       <c r="E25" s="13"/>
       <c r="F25" s="13" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
@@ -1992,14 +2145,14 @@
         <v>16</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D26" s="13" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E26" s="13"/>
       <c r="F26" s="13" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
@@ -2010,14 +2163,14 @@
         <v>16</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D27" s="13" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E27" s="13"/>
       <c r="F27" s="13" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
@@ -2028,14 +2181,14 @@
         <v>16</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D28" s="13" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E28" s="13"/>
       <c r="F28" s="13" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="57" x14ac:dyDescent="0.25">
@@ -2046,14 +2199,14 @@
         <v>16</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D29" s="13" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E29" s="13"/>
       <c r="F29" s="13" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
@@ -2064,14 +2217,14 @@
         <v>16</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D30" s="13" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E30" s="13"/>
       <c r="F30" s="13" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
@@ -2082,14 +2235,14 @@
         <v>16</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D31" s="13" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E31" s="13"/>
       <c r="F31" s="13" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -2100,16 +2253,16 @@
         <v>16</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D32" s="13" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E32" s="13" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F32" s="11" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -2120,14 +2273,14 @@
         <v>16</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D33" s="13" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E33" s="13"/>
       <c r="F33" s="11" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -2138,14 +2291,14 @@
         <v>16</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D34" s="13" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E34" s="13"/>
       <c r="F34" s="11" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -2156,14 +2309,14 @@
         <v>16</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D35" s="13" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E35" s="13"/>
       <c r="F35" s="11" t="s">
-        <v>122</v>
+        <v>142</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
@@ -2174,14 +2327,14 @@
         <v>16</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D36" s="13" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E36" s="13"/>
       <c r="F36" s="11" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -2192,14 +2345,14 @@
         <v>16</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D37" s="13" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E37" s="13"/>
       <c r="F37" s="11" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -2210,14 +2363,14 @@
         <v>16</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D38" s="13" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E38" s="13"/>
       <c r="F38" s="11" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -2228,14 +2381,14 @@
         <v>16</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D39" s="13" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E39" s="13"/>
       <c r="F39" s="11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -2246,14 +2399,14 @@
         <v>16</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D40" s="13" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E40" s="13"/>
       <c r="F40" s="11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -2264,14 +2417,14 @@
         <v>16</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D41" s="13" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E41" s="13"/>
       <c r="F41" s="11" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -2282,14 +2435,14 @@
         <v>16</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D42" s="13" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E42" s="13"/>
       <c r="F42" s="11" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -2300,10 +2453,10 @@
         <v>16</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D43" s="13" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E43" s="13"/>
       <c r="F43" s="11"/>
@@ -2316,10 +2469,10 @@
         <v>16</v>
       </c>
       <c r="C44" s="11" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D44" s="13" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E44" s="13"/>
       <c r="F44" s="11"/>
@@ -2332,14 +2485,14 @@
         <v>16</v>
       </c>
       <c r="C45" s="11" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="D45" s="13" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="E45" s="13"/>
       <c r="F45" s="11" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
@@ -2350,75 +2503,517 @@
         <v>16</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="D46" s="13" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="E46" s="13"/>
       <c r="F46" s="11" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="B47" s="11"/>
-      <c r="C47" s="11"/>
-      <c r="D47" s="13"/>
-      <c r="E47" s="13"/>
+        <v>7</v>
+      </c>
+      <c r="B47" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C47" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="D47" s="13" t="s">
+        <v>162</v>
+      </c>
+      <c r="E47" s="13" t="s">
+        <v>163</v>
+      </c>
       <c r="F47" s="11"/>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="B48" s="11"/>
-      <c r="C48" s="11"/>
-      <c r="D48" s="13"/>
-      <c r="E48" s="13"/>
+        <v>7</v>
+      </c>
+      <c r="B48" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C48" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="D48" s="13" t="s">
+        <v>164</v>
+      </c>
+      <c r="E48" s="13" t="s">
+        <v>165</v>
+      </c>
       <c r="F48" s="11"/>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="B49" s="11"/>
-      <c r="C49" s="11"/>
-      <c r="D49" s="13"/>
+        <v>7</v>
+      </c>
+      <c r="B49" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="C49" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D49" s="13" t="s">
+        <v>147</v>
+      </c>
       <c r="E49" s="13"/>
       <c r="F49" s="11"/>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="B50" s="11"/>
-      <c r="C50" s="11"/>
-      <c r="D50" s="13"/>
+        <v>7</v>
+      </c>
+      <c r="B50" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="C50" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="D50" s="13" t="s">
+        <v>149</v>
+      </c>
       <c r="E50" s="13"/>
       <c r="F50" s="11"/>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A51" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="B51" s="11"/>
-      <c r="C51" s="11"/>
-      <c r="D51" s="13"/>
+        <v>7</v>
+      </c>
+      <c r="B51" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="C51" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="D51" s="13" t="s">
+        <v>151</v>
+      </c>
       <c r="E51" s="13"/>
       <c r="F51" s="11"/>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="B52" s="11"/>
-      <c r="C52" s="11"/>
-      <c r="D52" s="13"/>
+        <v>7</v>
+      </c>
+      <c r="B52" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="C52" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="D52" s="13" t="s">
+        <v>153</v>
+      </c>
       <c r="E52" s="13"/>
       <c r="F52" s="11"/>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B53" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="C53" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="D53" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="E53" s="13"/>
+      <c r="F53" s="11"/>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B54" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="C54" s="11" t="s">
+        <v>156</v>
+      </c>
+      <c r="D54" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="E54" s="13" t="s">
+        <v>158</v>
+      </c>
+      <c r="F54" s="11"/>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B55" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="C55" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="D55" s="13" t="s">
+        <v>160</v>
+      </c>
+      <c r="E55" s="13"/>
+      <c r="F55" s="13"/>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B56" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="C56" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="D56" s="13" t="s">
+        <v>162</v>
+      </c>
+      <c r="E56" s="13" t="s">
+        <v>163</v>
+      </c>
+      <c r="F56" s="13"/>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B57" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="C57" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="D57" s="13" t="s">
+        <v>164</v>
+      </c>
+      <c r="E57" s="13" t="s">
+        <v>165</v>
+      </c>
+      <c r="F57" s="13"/>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B58" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="C58" s="11" t="s">
+        <v>166</v>
+      </c>
+      <c r="D58" s="13" t="s">
+        <v>167</v>
+      </c>
+      <c r="E58" s="13"/>
+      <c r="F58" s="13" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B59" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="C59" s="11" t="s">
+        <v>166</v>
+      </c>
+      <c r="D59" s="13" t="s">
+        <v>169</v>
+      </c>
+      <c r="E59" s="13"/>
+      <c r="F59" s="13" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B60" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="C60" s="11" t="s">
+        <v>171</v>
+      </c>
+      <c r="D60" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="E60" s="13"/>
+      <c r="F60" s="13" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B61" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="C61" s="11" t="s">
+        <v>171</v>
+      </c>
+      <c r="D61" s="13" t="s">
+        <v>173</v>
+      </c>
+      <c r="E61" s="13"/>
+      <c r="F61" s="13" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B62" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="C62" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="D62" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="E62" s="13" t="s">
+        <v>176</v>
+      </c>
+      <c r="F62" s="13" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B63" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="C63" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="D63" s="13" t="s">
+        <v>177</v>
+      </c>
+      <c r="E63" s="13" t="s">
+        <v>178</v>
+      </c>
+      <c r="F63" s="13" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B64" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="C64" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="D64" s="13" t="s">
+        <v>193</v>
+      </c>
+      <c r="E64" s="13" t="s">
+        <v>194</v>
+      </c>
+      <c r="F64" s="13" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A65" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B65" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="C65" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="D65" s="13" t="s">
+        <v>195</v>
+      </c>
+      <c r="E65" s="13" t="s">
+        <v>196</v>
+      </c>
+      <c r="F65" s="13" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A66" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B66" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="C66" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="D66" s="13" t="s">
+        <v>181</v>
+      </c>
+      <c r="E66" s="13" t="s">
+        <v>182</v>
+      </c>
+      <c r="F66" s="13" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A67" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B67" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="C67" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="D67" s="13" t="s">
+        <v>184</v>
+      </c>
+      <c r="E67" s="13" t="s">
+        <v>185</v>
+      </c>
+      <c r="F67" s="13" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A68" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B68" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="C68" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="D68" s="13" t="s">
+        <v>186</v>
+      </c>
+      <c r="E68" s="13" t="s">
+        <v>187</v>
+      </c>
+      <c r="F68" s="13" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A69" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B69" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="C69" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="D69" s="13" t="s">
+        <v>189</v>
+      </c>
+      <c r="E69" s="13" t="s">
+        <v>190</v>
+      </c>
+      <c r="F69" s="13" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A70" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B70" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="C70" s="11"/>
+      <c r="D70" s="13"/>
+      <c r="E70" s="13"/>
+      <c r="F70" s="13"/>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A71" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B71" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="C71" s="11"/>
+      <c r="D71" s="13"/>
+      <c r="E71" s="13"/>
+      <c r="F71" s="13"/>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A72" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B72" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="C72" s="11"/>
+      <c r="D72" s="13"/>
+      <c r="E72" s="13"/>
+      <c r="F72" s="13"/>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A73" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B73" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="C73" s="11"/>
+      <c r="D73" s="13"/>
+      <c r="E73" s="13"/>
+      <c r="F73" s="13"/>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A74" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B74" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="C74" s="11"/>
+      <c r="D74" s="13"/>
+      <c r="E74" s="13"/>
+      <c r="F74" s="13"/>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A75" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B75" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="C75" s="11"/>
+      <c r="D75" s="13"/>
+      <c r="E75" s="13"/>
+      <c r="F75" s="13"/>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A76" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B76" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="C76" s="11"/>
+      <c r="D76" s="13"/>
+      <c r="E76" s="13"/>
+      <c r="F76" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/pages/A787.xlsx
+++ b/pages/A787.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Downloads\Cabbase\pages\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DBA160C-FD40-4E9D-8232-A20AF20B7D7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B25F453F-AC47-4564-A645-F8820EC29F7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="562" uniqueCount="221">
   <si>
     <t>PART NUMBER (PN)</t>
   </si>
@@ -629,6 +629,78 @@
   </si>
   <si>
     <t>7233-1-10115WA4</t>
+  </si>
+  <si>
+    <t>F0492898</t>
+  </si>
+  <si>
+    <t>LITTERATURE POCKET</t>
+  </si>
+  <si>
+    <t>F0492897</t>
+  </si>
+  <si>
+    <t>LITTERATURE POCKET COVER</t>
+  </si>
+  <si>
+    <t>HEADPHONE - STRAP</t>
+  </si>
+  <si>
+    <t>HEADPHONE - HOOK</t>
+  </si>
+  <si>
+    <t>F0485717</t>
+  </si>
+  <si>
+    <t>G011169-571</t>
+  </si>
+  <si>
+    <t>F0485716</t>
+  </si>
+  <si>
+    <t>OTTOMAN ASSY</t>
+  </si>
+  <si>
+    <t>F0485574</t>
+  </si>
+  <si>
+    <t>F0486138</t>
+  </si>
+  <si>
+    <t>GHẾ 1AG &gt;&gt; 7AG</t>
+  </si>
+  <si>
+    <t>GHẾ 1DK &gt;&gt; 7DK</t>
+  </si>
+  <si>
+    <t>F0485572</t>
+  </si>
+  <si>
+    <t>FIXED ARMREST ASSY</t>
+  </si>
+  <si>
+    <t>F0485573</t>
+  </si>
+  <si>
+    <t>F0485575</t>
+  </si>
+  <si>
+    <t>F0485576</t>
+  </si>
+  <si>
+    <t>BED EXTENSION ASSY</t>
+  </si>
+  <si>
+    <t>F0530871</t>
+  </si>
+  <si>
+    <t>TRAY TABLE - BOTTOM COVER</t>
+  </si>
+  <si>
+    <t>EGRESS COVER ASSY</t>
+  </si>
+  <si>
+    <t>F0485114</t>
   </si>
 </sst>
 </file>
@@ -676,7 +748,7 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -753,11 +825,11 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1677,12 +1749,12 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:F76"/>
+  <dimension ref="A1:F99"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.140625" customWidth="1"/>
     <col min="2" max="2" width="20.28515625" customWidth="1"/>
-    <col min="3" max="3" width="28.42578125" customWidth="1"/>
+    <col min="3" max="3" width="37" customWidth="1"/>
     <col min="4" max="4" width="23" customWidth="1"/>
     <col min="5" max="5" width="33.7109375" customWidth="1"/>
     <col min="6" max="6" width="54.85546875" customWidth="1"/>
@@ -1716,13 +1788,13 @@
       <c r="B2" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="D2" s="13" t="s">
+      <c r="D2" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="E2" s="13" t="s">
+      <c r="E2" s="12" t="s">
         <v>18</v>
       </c>
       <c r="F2" s="11" t="s">
@@ -1736,13 +1808,13 @@
       <c r="B3" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="D3" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="E3" s="13" t="s">
+      <c r="E3" s="12" t="s">
         <v>23</v>
       </c>
       <c r="F3" s="11" t="s">
@@ -1756,13 +1828,13 @@
       <c r="B4" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="D4" s="13" t="s">
+      <c r="D4" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="E4" s="13" t="s">
+      <c r="E4" s="12" t="s">
         <v>48</v>
       </c>
       <c r="F4" s="11"/>
@@ -1777,10 +1849,10 @@
       <c r="C5" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="D5" s="13" t="s">
+      <c r="D5" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="E5" s="13"/>
+      <c r="E5" s="12"/>
       <c r="F5" s="11" t="s">
         <v>51</v>
       </c>
@@ -1795,10 +1867,10 @@
       <c r="C6" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="D6" s="13" t="s">
+      <c r="D6" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="E6" s="13"/>
+      <c r="E6" s="12"/>
       <c r="F6" s="11" t="s">
         <v>53</v>
       </c>
@@ -1813,10 +1885,10 @@
       <c r="C7" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="D7" s="13" t="s">
+      <c r="D7" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="E7" s="13" t="s">
+      <c r="E7" s="12" t="s">
         <v>56</v>
       </c>
       <c r="F7" s="11"/>
@@ -1831,10 +1903,10 @@
       <c r="C8" s="11" t="s">
         <v>180</v>
       </c>
-      <c r="D8" s="13" t="s">
+      <c r="D8" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="E8" s="13"/>
+      <c r="E8" s="12"/>
       <c r="F8" s="11" t="s">
         <v>58</v>
       </c>
@@ -1849,10 +1921,10 @@
       <c r="C9" s="11" t="s">
         <v>180</v>
       </c>
-      <c r="D9" s="13" t="s">
+      <c r="D9" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="E9" s="13"/>
+      <c r="E9" s="12"/>
       <c r="F9" s="11" t="s">
         <v>60</v>
       </c>
@@ -1867,10 +1939,10 @@
       <c r="C10" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="D10" s="13" t="s">
+      <c r="D10" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="E10" s="13"/>
+      <c r="E10" s="12"/>
       <c r="F10" s="11" t="s">
         <v>66</v>
       </c>
@@ -1885,10 +1957,10 @@
       <c r="C11" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="D11" s="13" t="s">
+      <c r="D11" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="E11" s="13"/>
+      <c r="E11" s="12"/>
       <c r="F11" s="11" t="s">
         <v>67</v>
       </c>
@@ -1903,10 +1975,10 @@
       <c r="C12" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="D12" s="13" t="s">
+      <c r="D12" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="E12" s="13"/>
+      <c r="E12" s="12"/>
       <c r="F12" s="11" t="s">
         <v>65</v>
       </c>
@@ -1921,10 +1993,10 @@
       <c r="C13" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="D13" s="13" t="s">
+      <c r="D13" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="E13" s="13"/>
+      <c r="E13" s="12"/>
       <c r="F13" s="11" t="s">
         <v>79</v>
       </c>
@@ -1939,10 +2011,10 @@
       <c r="C14" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="D14" s="13" t="s">
+      <c r="D14" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="E14" s="13"/>
+      <c r="E14" s="12"/>
       <c r="F14" s="11" t="s">
         <v>81</v>
       </c>
@@ -1957,10 +2029,10 @@
       <c r="C15" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="D15" s="13" t="s">
+      <c r="D15" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="E15" s="13"/>
+      <c r="E15" s="12"/>
       <c r="F15" s="11" t="s">
         <v>84</v>
       </c>
@@ -1975,15 +2047,15 @@
       <c r="C16" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="D16" s="13" t="s">
+      <c r="D16" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="E16" s="13"/>
+      <c r="E16" s="12"/>
       <c r="F16" s="11" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>7</v>
       </c>
@@ -1993,10 +2065,10 @@
       <c r="C17" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="D17" s="13" t="s">
+      <c r="D17" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="E17" s="13"/>
+      <c r="E17" s="12"/>
       <c r="F17" s="11" t="s">
         <v>86</v>
       </c>
@@ -2011,10 +2083,10 @@
       <c r="C18" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="D18" s="13" t="s">
+      <c r="D18" s="12" t="s">
         <v>90</v>
       </c>
-      <c r="E18" s="13"/>
+      <c r="E18" s="12"/>
       <c r="F18" s="11" t="s">
         <v>86</v>
       </c>
@@ -2029,10 +2101,10 @@
       <c r="C19" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="D19" s="13" t="s">
+      <c r="D19" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="E19" s="13"/>
+      <c r="E19" s="12"/>
       <c r="F19" s="11"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -2045,10 +2117,10 @@
       <c r="C20" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="D20" s="13" t="s">
+      <c r="D20" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="E20" s="13"/>
+      <c r="E20" s="12"/>
       <c r="F20" s="11"/>
     </row>
     <row r="21" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
@@ -2061,10 +2133,10 @@
       <c r="C21" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="D21" s="13" t="s">
+      <c r="D21" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="E21" s="13"/>
+      <c r="E21" s="12"/>
       <c r="F21" s="11"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -2077,10 +2149,10 @@
       <c r="C22" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="D22" s="13" t="s">
+      <c r="D22" s="12" t="s">
         <v>98</v>
       </c>
-      <c r="E22" s="13"/>
+      <c r="E22" s="12"/>
       <c r="F22" s="11"/>
     </row>
     <row r="23" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
@@ -2093,10 +2165,10 @@
       <c r="C23" s="11" t="s">
         <v>99</v>
       </c>
-      <c r="D23" s="13" t="s">
+      <c r="D23" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="E23" s="13"/>
+      <c r="E23" s="12"/>
       <c r="F23" s="11" t="s">
         <v>101</v>
       </c>
@@ -2111,11 +2183,11 @@
       <c r="C24" s="11" t="s">
         <v>99</v>
       </c>
-      <c r="D24" s="13" t="s">
+      <c r="D24" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="E24" s="13"/>
-      <c r="F24" s="13" t="s">
+      <c r="E24" s="12"/>
+      <c r="F24" s="12" t="s">
         <v>103</v>
       </c>
     </row>
@@ -2129,11 +2201,11 @@
       <c r="C25" s="11" t="s">
         <v>104</v>
       </c>
-      <c r="D25" s="13" t="s">
+      <c r="D25" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="E25" s="13"/>
-      <c r="F25" s="13" t="s">
+      <c r="E25" s="12"/>
+      <c r="F25" s="12" t="s">
         <v>112</v>
       </c>
     </row>
@@ -2147,11 +2219,11 @@
       <c r="C26" s="11" t="s">
         <v>104</v>
       </c>
-      <c r="D26" s="13" t="s">
+      <c r="D26" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="E26" s="13"/>
-      <c r="F26" s="13" t="s">
+      <c r="E26" s="12"/>
+      <c r="F26" s="12" t="s">
         <v>113</v>
       </c>
     </row>
@@ -2165,11 +2237,11 @@
       <c r="C27" s="11" t="s">
         <v>104</v>
       </c>
-      <c r="D27" s="13" t="s">
+      <c r="D27" s="12" t="s">
         <v>107</v>
       </c>
-      <c r="E27" s="13"/>
-      <c r="F27" s="13" t="s">
+      <c r="E27" s="12"/>
+      <c r="F27" s="12" t="s">
         <v>114</v>
       </c>
     </row>
@@ -2183,11 +2255,11 @@
       <c r="C28" s="11" t="s">
         <v>104</v>
       </c>
-      <c r="D28" s="13" t="s">
+      <c r="D28" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="E28" s="13"/>
-      <c r="F28" s="13" t="s">
+      <c r="E28" s="12"/>
+      <c r="F28" s="12" t="s">
         <v>115</v>
       </c>
     </row>
@@ -2201,11 +2273,11 @@
       <c r="C29" s="11" t="s">
         <v>104</v>
       </c>
-      <c r="D29" s="13" t="s">
+      <c r="D29" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="E29" s="13"/>
-      <c r="F29" s="13" t="s">
+      <c r="E29" s="12"/>
+      <c r="F29" s="12" t="s">
         <v>144</v>
       </c>
     </row>
@@ -2219,11 +2291,11 @@
       <c r="C30" s="11" t="s">
         <v>104</v>
       </c>
-      <c r="D30" s="13" t="s">
+      <c r="D30" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="E30" s="13"/>
-      <c r="F30" s="13" t="s">
+      <c r="E30" s="12"/>
+      <c r="F30" s="12" t="s">
         <v>116</v>
       </c>
     </row>
@@ -2237,11 +2309,11 @@
       <c r="C31" s="11" t="s">
         <v>104</v>
       </c>
-      <c r="D31" s="13" t="s">
+      <c r="D31" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="E31" s="13"/>
-      <c r="F31" s="13" t="s">
+      <c r="E31" s="12"/>
+      <c r="F31" s="12" t="s">
         <v>117</v>
       </c>
     </row>
@@ -2255,10 +2327,10 @@
       <c r="C32" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="D32" s="13" t="s">
+      <c r="D32" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="E32" s="13" t="s">
+      <c r="E32" s="12" t="s">
         <v>124</v>
       </c>
       <c r="F32" s="11" t="s">
@@ -2275,10 +2347,10 @@
       <c r="C33" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="D33" s="13" t="s">
+      <c r="D33" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="E33" s="13"/>
+      <c r="E33" s="12"/>
       <c r="F33" s="11" t="s">
         <v>119</v>
       </c>
@@ -2293,10 +2365,10 @@
       <c r="C34" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="D34" s="13" t="s">
+      <c r="D34" s="12" t="s">
         <v>107</v>
       </c>
-      <c r="E34" s="13"/>
+      <c r="E34" s="12"/>
       <c r="F34" s="11" t="s">
         <v>120</v>
       </c>
@@ -2311,10 +2383,10 @@
       <c r="C35" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="D35" s="13" t="s">
+      <c r="D35" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="E35" s="13"/>
+      <c r="E35" s="12"/>
       <c r="F35" s="11" t="s">
         <v>142</v>
       </c>
@@ -2329,10 +2401,10 @@
       <c r="C36" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="D36" s="13" t="s">
+      <c r="D36" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="E36" s="13"/>
+      <c r="E36" s="12"/>
       <c r="F36" s="11" t="s">
         <v>143</v>
       </c>
@@ -2347,10 +2419,10 @@
       <c r="C37" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="D37" s="13" t="s">
+      <c r="D37" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="E37" s="13"/>
+      <c r="E37" s="12"/>
       <c r="F37" s="11" t="s">
         <v>122</v>
       </c>
@@ -2365,10 +2437,10 @@
       <c r="C38" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="D38" s="13" t="s">
+      <c r="D38" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="E38" s="13"/>
+      <c r="E38" s="12"/>
       <c r="F38" s="11" t="s">
         <v>123</v>
       </c>
@@ -2383,10 +2455,10 @@
       <c r="C39" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="D39" s="13" t="s">
+      <c r="D39" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="E39" s="13"/>
+      <c r="E39" s="12"/>
       <c r="F39" s="11" t="s">
         <v>60</v>
       </c>
@@ -2401,10 +2473,10 @@
       <c r="C40" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="D40" s="13" t="s">
+      <c r="D40" s="12" t="s">
         <v>128</v>
       </c>
-      <c r="E40" s="13"/>
+      <c r="E40" s="12"/>
       <c r="F40" s="11" t="s">
         <v>60</v>
       </c>
@@ -2419,10 +2491,10 @@
       <c r="C41" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="D41" s="13" t="s">
+      <c r="D41" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="E41" s="13"/>
+      <c r="E41" s="12"/>
       <c r="F41" s="11" t="s">
         <v>135</v>
       </c>
@@ -2437,10 +2509,10 @@
       <c r="C42" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="D42" s="13" t="s">
+      <c r="D42" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="E42" s="13"/>
+      <c r="E42" s="12"/>
       <c r="F42" s="11" t="s">
         <v>134</v>
       </c>
@@ -2455,10 +2527,10 @@
       <c r="C43" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="D43" s="13" t="s">
+      <c r="D43" s="12" t="s">
         <v>129</v>
       </c>
-      <c r="E43" s="13"/>
+      <c r="E43" s="12"/>
       <c r="F43" s="11"/>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -2471,10 +2543,10 @@
       <c r="C44" s="11" t="s">
         <v>131</v>
       </c>
-      <c r="D44" s="13" t="s">
+      <c r="D44" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="E44" s="13"/>
+      <c r="E44" s="12"/>
       <c r="F44" s="11"/>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
@@ -2487,10 +2559,10 @@
       <c r="C45" s="11" t="s">
         <v>137</v>
       </c>
-      <c r="D45" s="13" t="s">
+      <c r="D45" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="E45" s="13"/>
+      <c r="E45" s="12"/>
       <c r="F45" s="11" t="s">
         <v>139</v>
       </c>
@@ -2505,10 +2577,10 @@
       <c r="C46" s="11" t="s">
         <v>137</v>
       </c>
-      <c r="D46" s="13" t="s">
+      <c r="D46" s="12" t="s">
         <v>140</v>
       </c>
-      <c r="E46" s="13"/>
+      <c r="E46" s="12"/>
       <c r="F46" s="11" t="s">
         <v>141</v>
       </c>
@@ -2523,10 +2595,10 @@
       <c r="C47" s="11" t="s">
         <v>161</v>
       </c>
-      <c r="D47" s="13" t="s">
+      <c r="D47" s="12" t="s">
         <v>162</v>
       </c>
-      <c r="E47" s="13" t="s">
+      <c r="E47" s="12" t="s">
         <v>163</v>
       </c>
       <c r="F47" s="11"/>
@@ -2541,10 +2613,10 @@
       <c r="C48" s="11" t="s">
         <v>161</v>
       </c>
-      <c r="D48" s="13" t="s">
+      <c r="D48" s="12" t="s">
         <v>164</v>
       </c>
-      <c r="E48" s="13" t="s">
+      <c r="E48" s="12" t="s">
         <v>165</v>
       </c>
       <c r="F48" s="11"/>
@@ -2559,10 +2631,10 @@
       <c r="C49" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="D49" s="13" t="s">
+      <c r="D49" s="12" t="s">
         <v>147</v>
       </c>
-      <c r="E49" s="13"/>
+      <c r="E49" s="12"/>
       <c r="F49" s="11"/>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
@@ -2575,10 +2647,10 @@
       <c r="C50" s="11" t="s">
         <v>148</v>
       </c>
-      <c r="D50" s="13" t="s">
+      <c r="D50" s="12" t="s">
         <v>149</v>
       </c>
-      <c r="E50" s="13"/>
+      <c r="E50" s="12"/>
       <c r="F50" s="11"/>
     </row>
     <row r="51" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
@@ -2591,10 +2663,10 @@
       <c r="C51" s="11" t="s">
         <v>150</v>
       </c>
-      <c r="D51" s="13" t="s">
+      <c r="D51" s="12" t="s">
         <v>151</v>
       </c>
-      <c r="E51" s="13"/>
+      <c r="E51" s="12"/>
       <c r="F51" s="11"/>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
@@ -2607,10 +2679,10 @@
       <c r="C52" s="11" t="s">
         <v>152</v>
       </c>
-      <c r="D52" s="13" t="s">
+      <c r="D52" s="12" t="s">
         <v>153</v>
       </c>
-      <c r="E52" s="13"/>
+      <c r="E52" s="12"/>
       <c r="F52" s="11"/>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
@@ -2623,10 +2695,10 @@
       <c r="C53" s="11" t="s">
         <v>154</v>
       </c>
-      <c r="D53" s="13" t="s">
+      <c r="D53" s="12" t="s">
         <v>155</v>
       </c>
-      <c r="E53" s="13"/>
+      <c r="E53" s="12"/>
       <c r="F53" s="11"/>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
@@ -2639,10 +2711,10 @@
       <c r="C54" s="11" t="s">
         <v>156</v>
       </c>
-      <c r="D54" s="13" t="s">
+      <c r="D54" s="12" t="s">
         <v>157</v>
       </c>
-      <c r="E54" s="13" t="s">
+      <c r="E54" s="12" t="s">
         <v>158</v>
       </c>
       <c r="F54" s="11"/>
@@ -2657,11 +2729,11 @@
       <c r="C55" s="11" t="s">
         <v>159</v>
       </c>
-      <c r="D55" s="13" t="s">
+      <c r="D55" s="12" t="s">
         <v>160</v>
       </c>
-      <c r="E55" s="13"/>
-      <c r="F55" s="13"/>
+      <c r="E55" s="12"/>
+      <c r="F55" s="12"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="11" t="s">
@@ -2673,13 +2745,13 @@
       <c r="C56" s="11" t="s">
         <v>161</v>
       </c>
-      <c r="D56" s="13" t="s">
+      <c r="D56" s="12" t="s">
         <v>162</v>
       </c>
-      <c r="E56" s="13" t="s">
+      <c r="E56" s="12" t="s">
         <v>163</v>
       </c>
-      <c r="F56" s="13"/>
+      <c r="F56" s="12"/>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="11" t="s">
@@ -2691,13 +2763,13 @@
       <c r="C57" s="11" t="s">
         <v>161</v>
       </c>
-      <c r="D57" s="13" t="s">
+      <c r="D57" s="12" t="s">
         <v>164</v>
       </c>
-      <c r="E57" s="13" t="s">
+      <c r="E57" s="12" t="s">
         <v>165</v>
       </c>
-      <c r="F57" s="13"/>
+      <c r="F57" s="12"/>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="11" t="s">
@@ -2709,11 +2781,11 @@
       <c r="C58" s="11" t="s">
         <v>166</v>
       </c>
-      <c r="D58" s="13" t="s">
+      <c r="D58" s="12" t="s">
         <v>167</v>
       </c>
-      <c r="E58" s="13"/>
-      <c r="F58" s="13" t="s">
+      <c r="E58" s="12"/>
+      <c r="F58" s="12" t="s">
         <v>168</v>
       </c>
     </row>
@@ -2727,11 +2799,11 @@
       <c r="C59" s="11" t="s">
         <v>166</v>
       </c>
-      <c r="D59" s="13" t="s">
+      <c r="D59" s="12" t="s">
         <v>169</v>
       </c>
-      <c r="E59" s="13"/>
-      <c r="F59" s="13" t="s">
+      <c r="E59" s="12"/>
+      <c r="F59" s="12" t="s">
         <v>170</v>
       </c>
     </row>
@@ -2745,11 +2817,11 @@
       <c r="C60" s="11" t="s">
         <v>171</v>
       </c>
-      <c r="D60" s="13" t="s">
+      <c r="D60" s="12" t="s">
         <v>172</v>
       </c>
-      <c r="E60" s="13"/>
-      <c r="F60" s="13" t="s">
+      <c r="E60" s="12"/>
+      <c r="F60" s="12" t="s">
         <v>168</v>
       </c>
     </row>
@@ -2763,11 +2835,11 @@
       <c r="C61" s="11" t="s">
         <v>171</v>
       </c>
-      <c r="D61" s="13" t="s">
+      <c r="D61" s="12" t="s">
         <v>173</v>
       </c>
-      <c r="E61" s="13"/>
-      <c r="F61" s="13" t="s">
+      <c r="E61" s="12"/>
+      <c r="F61" s="12" t="s">
         <v>170</v>
       </c>
     </row>
@@ -2781,13 +2853,13 @@
       <c r="C62" s="11" t="s">
         <v>192</v>
       </c>
-      <c r="D62" s="13" t="s">
+      <c r="D62" s="12" t="s">
         <v>174</v>
       </c>
-      <c r="E62" s="13" t="s">
+      <c r="E62" s="12" t="s">
         <v>176</v>
       </c>
-      <c r="F62" s="13" t="s">
+      <c r="F62" s="12" t="s">
         <v>175</v>
       </c>
     </row>
@@ -2801,13 +2873,13 @@
       <c r="C63" s="11" t="s">
         <v>192</v>
       </c>
-      <c r="D63" s="13" t="s">
+      <c r="D63" s="12" t="s">
         <v>177</v>
       </c>
-      <c r="E63" s="13" t="s">
+      <c r="E63" s="12" t="s">
         <v>178</v>
       </c>
-      <c r="F63" s="13" t="s">
+      <c r="F63" s="12" t="s">
         <v>179</v>
       </c>
     </row>
@@ -2821,13 +2893,13 @@
       <c r="C64" s="11" t="s">
         <v>192</v>
       </c>
-      <c r="D64" s="13" t="s">
+      <c r="D64" s="12" t="s">
         <v>193</v>
       </c>
-      <c r="E64" s="13" t="s">
+      <c r="E64" s="12" t="s">
         <v>194</v>
       </c>
-      <c r="F64" s="13" t="s">
+      <c r="F64" s="12" t="s">
         <v>188</v>
       </c>
     </row>
@@ -2841,13 +2913,13 @@
       <c r="C65" s="11" t="s">
         <v>192</v>
       </c>
-      <c r="D65" s="13" t="s">
+      <c r="D65" s="12" t="s">
         <v>195</v>
       </c>
-      <c r="E65" s="13" t="s">
+      <c r="E65" s="12" t="s">
         <v>196</v>
       </c>
-      <c r="F65" s="13" t="s">
+      <c r="F65" s="12" t="s">
         <v>191</v>
       </c>
     </row>
@@ -2861,13 +2933,13 @@
       <c r="C66" s="11" t="s">
         <v>183</v>
       </c>
-      <c r="D66" s="13" t="s">
+      <c r="D66" s="12" t="s">
         <v>181</v>
       </c>
-      <c r="E66" s="13" t="s">
+      <c r="E66" s="12" t="s">
         <v>182</v>
       </c>
-      <c r="F66" s="13" t="s">
+      <c r="F66" s="12" t="s">
         <v>175</v>
       </c>
     </row>
@@ -2881,13 +2953,13 @@
       <c r="C67" s="11" t="s">
         <v>183</v>
       </c>
-      <c r="D67" s="13" t="s">
+      <c r="D67" s="12" t="s">
         <v>184</v>
       </c>
-      <c r="E67" s="13" t="s">
+      <c r="E67" s="12" t="s">
         <v>185</v>
       </c>
-      <c r="F67" s="13" t="s">
+      <c r="F67" s="12" t="s">
         <v>179</v>
       </c>
     </row>
@@ -2901,13 +2973,13 @@
       <c r="C68" s="11" t="s">
         <v>183</v>
       </c>
-      <c r="D68" s="13" t="s">
+      <c r="D68" s="12" t="s">
         <v>186</v>
       </c>
-      <c r="E68" s="13" t="s">
+      <c r="E68" s="12" t="s">
         <v>187</v>
       </c>
-      <c r="F68" s="13" t="s">
+      <c r="F68" s="12" t="s">
         <v>188</v>
       </c>
     </row>
@@ -2921,13 +2993,13 @@
       <c r="C69" s="11" t="s">
         <v>183</v>
       </c>
-      <c r="D69" s="13" t="s">
+      <c r="D69" s="12" t="s">
         <v>189</v>
       </c>
-      <c r="E69" s="13" t="s">
+      <c r="E69" s="12" t="s">
         <v>190</v>
       </c>
-      <c r="F69" s="13" t="s">
+      <c r="F69" s="12" t="s">
         <v>191</v>
       </c>
     </row>
@@ -2938,22 +3010,30 @@
       <c r="B70" s="11" t="s">
         <v>145</v>
       </c>
-      <c r="C70" s="11"/>
-      <c r="D70" s="13"/>
-      <c r="E70" s="13"/>
-      <c r="F70" s="13"/>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C70" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="D70" s="12" t="s">
+        <v>197</v>
+      </c>
+      <c r="E70" s="12"/>
+      <c r="F70" s="12"/>
+    </row>
+    <row r="71" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A71" s="11" t="s">
         <v>7</v>
       </c>
       <c r="B71" s="11" t="s">
         <v>145</v>
       </c>
-      <c r="C71" s="11"/>
-      <c r="D71" s="13"/>
-      <c r="E71" s="13"/>
-      <c r="F71" s="13"/>
+      <c r="C71" s="11" t="s">
+        <v>200</v>
+      </c>
+      <c r="D71" s="12" t="s">
+        <v>199</v>
+      </c>
+      <c r="E71" s="12"/>
+      <c r="F71" s="12"/>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="11" t="s">
@@ -2962,10 +3042,16 @@
       <c r="B72" s="11" t="s">
         <v>145</v>
       </c>
-      <c r="C72" s="11"/>
-      <c r="D72" s="13"/>
-      <c r="E72" s="13"/>
-      <c r="F72" s="13"/>
+      <c r="C72" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="D72" s="12" t="s">
+        <v>203</v>
+      </c>
+      <c r="E72" s="12" t="s">
+        <v>204</v>
+      </c>
+      <c r="F72" s="12"/>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="11" t="s">
@@ -2974,10 +3060,14 @@
       <c r="B73" s="11" t="s">
         <v>145</v>
       </c>
-      <c r="C73" s="11"/>
-      <c r="D73" s="13"/>
-      <c r="E73" s="13"/>
-      <c r="F73" s="13"/>
+      <c r="C73" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="D73" s="12" t="s">
+        <v>205</v>
+      </c>
+      <c r="E73" s="12"/>
+      <c r="F73" s="12"/>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="11" t="s">
@@ -2986,10 +3076,16 @@
       <c r="B74" s="11" t="s">
         <v>145</v>
       </c>
-      <c r="C74" s="11"/>
-      <c r="D74" s="13"/>
-      <c r="E74" s="13"/>
-      <c r="F74" s="13"/>
+      <c r="C74" s="11" t="s">
+        <v>206</v>
+      </c>
+      <c r="D74" s="12" t="s">
+        <v>207</v>
+      </c>
+      <c r="E74" s="12"/>
+      <c r="F74" s="12" t="s">
+        <v>209</v>
+      </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="11" t="s">
@@ -2998,10 +3094,16 @@
       <c r="B75" s="11" t="s">
         <v>145</v>
       </c>
-      <c r="C75" s="11"/>
-      <c r="D75" s="13"/>
-      <c r="E75" s="13"/>
-      <c r="F75" s="13"/>
+      <c r="C75" s="11" t="s">
+        <v>206</v>
+      </c>
+      <c r="D75" s="12" t="s">
+        <v>208</v>
+      </c>
+      <c r="E75" s="12"/>
+      <c r="F75" s="12" t="s">
+        <v>210</v>
+      </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="11" t="s">
@@ -3010,10 +3112,318 @@
       <c r="B76" s="11" t="s">
         <v>145</v>
       </c>
-      <c r="C76" s="11"/>
-      <c r="D76" s="13"/>
-      <c r="E76" s="13"/>
-      <c r="F76" s="13"/>
+      <c r="C76" s="11" t="s">
+        <v>212</v>
+      </c>
+      <c r="D76" s="11" t="s">
+        <v>211</v>
+      </c>
+      <c r="E76" s="11"/>
+      <c r="F76" s="12" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A77" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B77" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="C77" s="11" t="s">
+        <v>212</v>
+      </c>
+      <c r="D77" s="11" t="s">
+        <v>213</v>
+      </c>
+      <c r="E77" s="11"/>
+      <c r="F77" s="12" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A78" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B78" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="C78" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="D78" s="11" t="s">
+        <v>214</v>
+      </c>
+      <c r="E78" s="11"/>
+      <c r="F78" s="12" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A79" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B79" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="C79" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="D79" s="11" t="s">
+        <v>215</v>
+      </c>
+      <c r="E79" s="11"/>
+      <c r="F79" s="12" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A80" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B80" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="C80" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="D80" s="11" t="s">
+        <v>217</v>
+      </c>
+      <c r="E80" s="11"/>
+      <c r="F80" s="11"/>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A81" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B81" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="C81" s="11" t="s">
+        <v>219</v>
+      </c>
+      <c r="D81" s="11" t="s">
+        <v>220</v>
+      </c>
+      <c r="E81" s="11"/>
+      <c r="F81" s="11"/>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A82" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B82" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="C82" s="11"/>
+      <c r="D82" s="11"/>
+      <c r="E82" s="11"/>
+      <c r="F82" s="11"/>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A83" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B83" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="C83" s="11"/>
+      <c r="D83" s="11"/>
+      <c r="E83" s="11"/>
+      <c r="F83" s="11"/>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A84" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B84" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="C84" s="11"/>
+      <c r="D84" s="11"/>
+      <c r="E84" s="11"/>
+      <c r="F84" s="11"/>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A85" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B85" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="C85" s="11"/>
+      <c r="D85" s="11"/>
+      <c r="E85" s="11"/>
+      <c r="F85" s="11"/>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A86" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B86" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="C86" s="11"/>
+      <c r="D86" s="11"/>
+      <c r="E86" s="11"/>
+      <c r="F86" s="11"/>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A87" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B87" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="C87" s="11"/>
+      <c r="D87" s="11"/>
+      <c r="E87" s="11"/>
+      <c r="F87" s="11"/>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A88" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B88" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="C88" s="11"/>
+      <c r="D88" s="11"/>
+      <c r="E88" s="11"/>
+      <c r="F88" s="11"/>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A89" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B89" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="C89" s="11"/>
+      <c r="D89" s="11"/>
+      <c r="E89" s="11"/>
+      <c r="F89" s="11"/>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A90" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B90" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="C90" s="11"/>
+      <c r="D90" s="11"/>
+      <c r="E90" s="11"/>
+      <c r="F90" s="11"/>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A91" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B91" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="C91" s="11"/>
+      <c r="D91" s="11"/>
+      <c r="E91" s="11"/>
+      <c r="F91" s="11"/>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A92" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B92" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="C92" s="11"/>
+      <c r="D92" s="11"/>
+      <c r="E92" s="11"/>
+      <c r="F92" s="11"/>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A93" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B93" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="C93" s="11"/>
+      <c r="D93" s="11"/>
+      <c r="E93" s="11"/>
+      <c r="F93" s="11"/>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A94" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B94" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="C94" s="11"/>
+      <c r="D94" s="11"/>
+      <c r="E94" s="11"/>
+      <c r="F94" s="11"/>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A95" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B95" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="C95" s="11"/>
+      <c r="D95" s="11"/>
+      <c r="E95" s="11"/>
+      <c r="F95" s="11"/>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A96" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B96" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="C96" s="11"/>
+      <c r="D96" s="11"/>
+      <c r="E96" s="11"/>
+      <c r="F96" s="11"/>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A97" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B97" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="C97" s="11"/>
+      <c r="D97" s="11"/>
+      <c r="E97" s="11"/>
+      <c r="F97" s="11"/>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A98" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B98" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="C98" s="11"/>
+      <c r="D98" s="11"/>
+      <c r="E98" s="11"/>
+      <c r="F98" s="11"/>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A99" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B99" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="C99" s="11"/>
+      <c r="D99" s="11"/>
+      <c r="E99" s="11"/>
+      <c r="F99" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
